--- a/tests/js/fixtures/legacy_small.xlsx
+++ b/tests/js/fixtures/legacy_small.xlsx
@@ -11,6 +11,7 @@
     <sheet name="1. 상품 &amp; 캠페인 매핑" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. 일별 광고 실적 입력" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. 일별 매출 실적 입력" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4. 광고 장부확인" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E7"/>
+  <dimension ref="B2:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -537,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Q7"/>
+  <dimension ref="B2:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -752,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:R8"/>
+  <dimension ref="B2:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -1041,9 +1042,1057 @@
       <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>캠페인 이름만 기입하면 자동 계산 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>45811</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>45812</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>45813</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>45814</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>45815</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>45816</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>45818</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>6월 합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>전체 순이익 (광고비제외)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1_버킷햇_240%</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>목표효율</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>광고수익률</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.6769</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>광고예산</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>70000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>집행 광고비*10%</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>73965.10000000001</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CPC 단가</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>439.48</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>노출수</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>51328</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>클릭률</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>전환율</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>광고 전환 판매 수</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>자연 판매 수</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>실제 판매 수</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>12</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>광고 마진</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>72000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>순이익 (광고비제외)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-1965.1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2_조거팬츠_238%</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>목표효율</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>광고수익률</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.694</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>광고예산</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>80000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>집행 광고비*10%</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>77360.8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CPC 단가</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>468.85</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>노출수</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>24384</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>클릭률</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>전환율</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>광고 전환 판매 수</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>23</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>자연 판매 수</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>실제 판매 수</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>22</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>광고 마진</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>142000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>순이익 (광고비제외)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>64639.2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>이곳에 광고캠페인명을 입력해 주세요</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>목표효율</t>
+        </is>
       </c>
     </row>
   </sheetData>
